--- a/data/trans_orig/IP21-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94206</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101573</t>
+          <t>101816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89494</t>
+          <t>88886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95657</t>
+          <t>95610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186935</t>
+          <t>187336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196356</t>
+          <t>196561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77800</t>
+          <t>77527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84914</t>
+          <t>84897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78770</t>
+          <t>78995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85132</t>
+          <t>85233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159517</t>
+          <t>159576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168878</t>
+          <t>168815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89456</t>
+          <t>89073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>96686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155747</t>
+          <t>155366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163981</t>
+          <t>163989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24472</t>
+          <t>24585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187697</t>
+          <t>188512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196872</t>
+          <t>196935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186679</t>
+          <t>186037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196660</t>
+          <t>196242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378335</t>
+          <t>378222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391570</t>
+          <t>391488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96665</t>
+          <t>97013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102918</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117772</t>
+          <t>117224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125295</t>
+          <t>125326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217596</t>
+          <t>218420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227542</t>
+          <t>227199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>69987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74255</t>
+          <t>74263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>63904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70924</t>
+          <t>70546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136060</t>
+          <t>136319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144133</t>
+          <t>144257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40985</t>
+          <t>41305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>44145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66178</t>
+          <t>66782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>606803</t>
+          <t>607098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621810</t>
+          <t>622506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>643618</t>
+          <t>643298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>660953</t>
+          <t>660985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1257281</t>
+          <t>1256677</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1279815</t>
+          <t>1279314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85715</t>
+          <t>86014</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83443</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88168</t>
+          <t>88164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171846</t>
+          <t>171767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177578</t>
+          <t>177593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>87972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92640</t>
+          <t>92648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88929</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95330</t>
+          <t>95341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180154</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187321</t>
+          <t>187312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85535</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78196</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84355</t>
+          <t>84372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161673</t>
+          <t>161880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169727</t>
+          <t>169714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33764</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184444</t>
+          <t>183697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197227</t>
+          <t>196636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210344</t>
+          <t>210280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>221740</t>
+          <t>221688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400449</t>
+          <t>399933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416009</t>
+          <t>416019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139493</t>
+          <t>140132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147148</t>
+          <t>147129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128172</t>
+          <t>127643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137248</t>
+          <t>136924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>270591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282583</t>
+          <t>282642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49141</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64453</t>
+          <t>64215</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71472</t>
+          <t>71385</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116550</t>
+          <t>115969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124099</t>
+          <t>124166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>41158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46171</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70532</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643804</t>
+          <t>643144</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659932</t>
+          <t>659530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671307</t>
+          <t>671882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690069</t>
+          <t>689725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1321052</t>
+          <t>1321136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1345413</t>
+          <t>1346179</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77497</t>
+          <t>77953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82568</t>
+          <t>82561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94786</t>
+          <t>95120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99245</t>
+          <t>99252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175046</t>
+          <t>174846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181222</t>
+          <t>181461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99202</t>
+          <t>98707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104583</t>
+          <t>104500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104272</t>
+          <t>104280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>111185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206232</t>
+          <t>205811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>214676</t>
+          <t>214787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57166</t>
+          <t>57067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66667</t>
+          <t>66329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73965</t>
+          <t>73575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126852</t>
+          <t>126722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134636</t>
+          <t>134459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213322</t>
+          <t>212944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220734</t>
+          <t>220655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201966</t>
+          <t>201330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209378</t>
+          <t>208826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>418728</t>
+          <t>417882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>428799</t>
+          <t>428556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125900</t>
+          <t>125907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133495</t>
+          <t>133593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131591</t>
+          <t>131343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140613</t>
+          <t>140671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260537</t>
+          <t>261654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272106</t>
+          <t>272925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54674</t>
+          <t>55076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60534</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>64588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121703</t>
+          <t>121516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127771</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29222</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30610</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643481</t>
+          <t>643629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657067</t>
+          <t>656529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680515</t>
+          <t>681022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>696123</t>
+          <t>695634</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1329106</t>
+          <t>1329698</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1349406</t>
+          <t>1349518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98694</t>
+          <t>99285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104013</t>
+          <t>104040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130484</t>
+          <t>130473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136035</t>
+          <t>136232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231961</t>
+          <t>232621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239627</t>
+          <t>239323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88074</t>
+          <t>88237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>92354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183260</t>
+          <t>183042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189093</t>
+          <t>189145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>60563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111621</t>
+          <t>111535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115374</t>
+          <t>115364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212648</t>
+          <t>212999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217162</t>
+          <t>217159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207087</t>
+          <t>207013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216432</t>
+          <t>216337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>422197</t>
+          <t>421696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>432706</t>
+          <t>432944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113449</t>
+          <t>113016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118776</t>
+          <t>118767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155118</t>
+          <t>155186</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161661</t>
+          <t>161605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271843</t>
+          <t>272223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279699</t>
+          <t>279770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67712</t>
+          <t>68138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136604</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30179</t>
+          <t>31503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>642088</t>
+          <t>641983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651552</t>
+          <t>651763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>729888</t>
+          <t>729449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>741906</t>
+          <t>741656</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1375968</t>
+          <t>1374644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1390913</t>
+          <t>1390697</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
